--- a/data/base/Backlog_33.xlsx
+++ b/data/base/Backlog_33.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F0B7D8-0ECA-45E0-9EE7-CF282EA571F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC68752-E461-4711-91A6-C93F8B27E6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F7992F62-A5A5-4D5B-880A-726CB0342990}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F7992F62-A5A5-4D5B-880A-726CB0342990}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="35">
   <si>
     <t>Status</t>
   </si>
@@ -77,9 +77,6 @@
   </si>
   <si>
     <t>Jose Ortiz</t>
-  </si>
-  <si>
-    <t>Kaua Barros</t>
   </si>
   <si>
     <t>Setor</t>
@@ -137,6 +134,15 @@
   </si>
   <si>
     <t>Willian Rios</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
+  </si>
+  <si>
+    <t>Lucas Fonseca</t>
+  </si>
+  <si>
+    <t>Eduardo Silva</t>
   </si>
 </sst>
 </file>
@@ -1073,42 +1079,42 @@
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>8</v>
@@ -1135,7 +1141,7 @@
         <v>46258</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>10</v>
@@ -1143,7 +1149,7 @@
     </row>
     <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>8</v>
@@ -1170,7 +1176,7 @@
         <v>46258</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>10</v>
@@ -1178,7 +1184,7 @@
     </row>
     <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>10</v>
@@ -1205,7 +1211,7 @@
         <v>46258</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>10</v>
@@ -1213,7 +1219,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>5</v>
@@ -1240,7 +1246,7 @@
         <v>46258</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>10</v>
@@ -1248,7 +1254,7 @@
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>5</v>
@@ -1275,7 +1281,7 @@
         <v>46258</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>10</v>
@@ -1283,7 +1289,7 @@
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>5</v>
@@ -1310,7 +1316,7 @@
         <v>46258</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>10</v>
@@ -1318,10 +1324,10 @@
     </row>
     <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C8" s="1">
         <v>2026</v>
@@ -1345,7 +1351,7 @@
         <v>46258</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>10</v>
@@ -1353,7 +1359,7 @@
     </row>
     <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>5</v>
@@ -1380,7 +1386,7 @@
         <v>46258</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>10</v>
@@ -1388,7 +1394,7 @@
     </row>
     <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>5</v>
@@ -1415,7 +1421,7 @@
         <v>46258</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>10</v>
@@ -1423,7 +1429,7 @@
     </row>
     <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>5</v>
@@ -1450,7 +1456,7 @@
         <v>46258</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>10</v>
@@ -1458,7 +1464,7 @@
     </row>
     <row r="12" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>5</v>
@@ -1485,7 +1491,7 @@
         <v>46258</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>10</v>
@@ -1493,7 +1499,7 @@
     </row>
     <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>4</v>
@@ -1520,7 +1526,7 @@
         <v>46258</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>10</v>
@@ -1528,7 +1534,7 @@
     </row>
     <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>4</v>
@@ -1555,7 +1561,7 @@
         <v>46258</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>10</v>
@@ -1563,7 +1569,7 @@
     </row>
     <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>4</v>
@@ -1590,7 +1596,7 @@
         <v>46258</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>10</v>
@@ -1598,7 +1604,7 @@
     </row>
     <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>2</v>
@@ -1625,7 +1631,7 @@
         <v>46258</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>10</v>
@@ -1633,7 +1639,7 @@
     </row>
     <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>2</v>
@@ -1660,7 +1666,7 @@
         <v>46258</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>10</v>
@@ -1668,7 +1674,7 @@
     </row>
     <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>2</v>
@@ -1695,7 +1701,7 @@
         <v>46258</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>10</v>
@@ -1703,7 +1709,7 @@
     </row>
     <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>12</v>
@@ -1730,7 +1736,7 @@
         <v>46258</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>10</v>
@@ -1738,7 +1744,7 @@
     </row>
     <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>12</v>
@@ -1765,7 +1771,7 @@
         <v>46258</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>10</v>
@@ -1773,10 +1779,10 @@
     </row>
     <row r="21" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C21" s="1">
         <v>2026</v>
@@ -1800,7 +1806,7 @@
         <v>46258</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>10</v>
@@ -1808,7 +1814,7 @@
     </row>
     <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>7</v>
@@ -1835,7 +1841,7 @@
         <v>46258</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>10</v>
@@ -1843,7 +1849,7 @@
     </row>
     <row r="23" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>7</v>
@@ -1870,7 +1876,7 @@
         <v>46258</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>10</v>
@@ -1878,7 +1884,7 @@
     </row>
     <row r="24" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>7</v>
@@ -1905,7 +1911,7 @@
         <v>46258</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>10</v>
@@ -1913,7 +1919,7 @@
     </row>
     <row r="25" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>7</v>
@@ -1940,7 +1946,7 @@
         <v>46258</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>10</v>
@@ -1948,7 +1954,7 @@
     </row>
     <row r="26" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>1</v>
@@ -1975,7 +1981,7 @@
         <v>46258</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>10</v>
@@ -1983,7 +1989,7 @@
     </row>
     <row r="27" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>7</v>
@@ -2010,7 +2016,7 @@
         <v>46258</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>10</v>
@@ -2018,7 +2024,7 @@
     </row>
     <row r="28" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>7</v>
@@ -2045,7 +2051,7 @@
         <v>46258</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>10</v>
@@ -2053,7 +2059,7 @@
     </row>
     <row r="29" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>7</v>
@@ -2080,7 +2086,7 @@
         <v>46258</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>10</v>
@@ -2088,7 +2094,7 @@
     </row>
     <row r="30" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>7</v>
@@ -2115,7 +2121,7 @@
         <v>46258</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>10</v>
@@ -2123,7 +2129,7 @@
     </row>
     <row r="31" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>6</v>
@@ -2150,7 +2156,7 @@
         <v>46258</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>10</v>
@@ -2158,7 +2164,7 @@
     </row>
     <row r="32" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>6</v>
@@ -2185,7 +2191,7 @@
         <v>46258</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>10</v>
@@ -2193,7 +2199,7 @@
     </row>
     <row r="33" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>6</v>
@@ -2220,7 +2226,7 @@
         <v>46258</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>10</v>
@@ -2228,7 +2234,7 @@
     </row>
     <row r="34" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>6</v>
@@ -2255,7 +2261,7 @@
         <v>46258</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>10</v>
@@ -2263,7 +2269,7 @@
     </row>
     <row r="35" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>6</v>
@@ -2290,7 +2296,7 @@
         <v>46258</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>10</v>
@@ -2298,7 +2304,7 @@
     </row>
     <row r="36" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>1</v>
@@ -2325,7 +2331,7 @@
         <v>46258</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>10</v>
@@ -2333,7 +2339,7 @@
     </row>
     <row r="37" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>1</v>
@@ -2360,7 +2366,7 @@
         <v>46258</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>10</v>
@@ -2368,7 +2374,7 @@
     </row>
     <row r="38" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>1</v>
@@ -2395,7 +2401,7 @@
         <v>46258</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K38" s="1" t="s">
         <v>10</v>
@@ -2403,7 +2409,7 @@
     </row>
     <row r="39" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>9</v>
@@ -2430,7 +2436,7 @@
         <v>46258</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K39" s="1" t="s">
         <v>10</v>
@@ -2490,45 +2496,45 @@
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" s="1">
         <v>2026</v>
@@ -2552,18 +2558,18 @@
         <v>46258</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1">
         <v>2026</v>
@@ -2587,18 +2593,18 @@
         <v>46258</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1">
         <v>2026</v>
@@ -2622,18 +2628,18 @@
         <v>46258</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1">
         <v>2026</v>
@@ -2657,18 +2663,18 @@
         <v>46258</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1">
         <v>2026</v>
@@ -2692,18 +2698,18 @@
         <v>46258</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1">
         <v>2026</v>
@@ -2727,18 +2733,18 @@
         <v>46258</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1">
         <v>2026</v>
@@ -2762,18 +2768,18 @@
         <v>46258</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1">
         <v>2026</v>
@@ -2797,18 +2803,18 @@
         <v>46258</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1">
         <v>2026</v>
@@ -2832,18 +2838,18 @@
         <v>46258</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" s="1">
         <v>2026</v>
@@ -2867,18 +2873,18 @@
         <v>46258</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" s="1">
         <v>2026</v>
@@ -2902,15 +2908,15 @@
         <v>46258</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>11</v>
@@ -2937,15 +2943,15 @@
         <v>46258</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>11</v>
@@ -2972,18 +2978,18 @@
         <v>46258</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="1">
         <v>2026</v>
@@ -3007,18 +3013,18 @@
         <v>46258</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="1">
         <v>2026</v>
@@ -3042,15 +3048,15 @@
         <v>46258</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:11 16384:16384" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>3</v>
@@ -3077,18 +3083,18 @@
         <v>46258</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:11 16384:16384" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C18" s="1">
         <v>2026</v>
@@ -3112,15 +3118,15 @@
         <v>46258</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:11 16384:16384" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>3</v>
@@ -3147,15 +3153,15 @@
         <v>46258</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:11 16384:16384" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>3</v>
@@ -3182,15 +3188,15 @@
         <v>46258</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:11 16384:16384" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>3</v>
@@ -3217,15 +3223,15 @@
         <v>46258</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:11 16384:16384" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>3</v>
@@ -3252,15 +3258,15 @@
         <v>46258</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:11 16384:16384" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>3</v>
@@ -3287,15 +3293,15 @@
         <v>46258</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:11 16384:16384" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -3322,18 +3328,18 @@
         <v>46258</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:11 16384:16384" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C25" s="1">
         <v>2026</v>
@@ -3357,18 +3363,18 @@
         <v>46258</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:11 16384:16384" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C26" s="1">
         <v>2026</v>
@@ -3392,18 +3398,18 @@
         <v>46258</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:11 16384:16384" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C27" s="1">
         <v>2026</v>
@@ -3427,10 +3433,10 @@
         <v>46258</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="XFD27" s="3">
         <f>SUM(C27:XFC27)</f>
